--- a/Laporan Grade Induk/grade 29 sep.xlsx
+++ b/Laporan Grade Induk/grade 29 sep.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xenov\Downloads\cekbarkot\Laporan Grade Induk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2E92E554-7EA5-4C82-A606-562A5CC60A6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4D8C1320-2D5B-465D-8DE1-DB8D9805D0BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,8 +18,19 @@
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Sheet1!$1:$4</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -488,9 +499,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
   <dimension ref="A1:G1004"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -564,7 +572,9 @@
       <c r="D5" s="6">
         <v>381362</v>
       </c>
-      <c r="E5" s="7"/>
+      <c r="E5" s="7">
+        <v>45</v>
+      </c>
       <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -580,7 +590,9 @@
       <c r="D6" s="6">
         <v>381098</v>
       </c>
-      <c r="E6" s="7"/>
+      <c r="E6" s="7">
+        <v>50</v>
+      </c>
       <c r="F6" s="8"/>
     </row>
     <row r="7" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -596,7 +608,9 @@
       <c r="D7" s="6">
         <v>381099</v>
       </c>
-      <c r="E7" s="7"/>
+      <c r="E7" s="7">
+        <v>46</v>
+      </c>
       <c r="F7" s="8"/>
     </row>
     <row r="8" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -612,7 +626,9 @@
       <c r="D8" s="6">
         <v>381097</v>
       </c>
-      <c r="E8" s="7"/>
+      <c r="E8" s="7">
+        <v>44</v>
+      </c>
       <c r="F8" s="8"/>
     </row>
     <row r="9" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -628,7 +644,9 @@
       <c r="D9" s="6">
         <v>381372</v>
       </c>
-      <c r="E9" s="7"/>
+      <c r="E9" s="7">
+        <v>37</v>
+      </c>
       <c r="F9" s="8"/>
     </row>
     <row r="10" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -644,7 +662,9 @@
       <c r="D10" s="6">
         <v>381083</v>
       </c>
-      <c r="E10" s="7"/>
+      <c r="E10" s="7">
+        <v>50</v>
+      </c>
       <c r="F10" s="8"/>
     </row>
     <row r="11" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -660,7 +680,9 @@
       <c r="D11" s="6">
         <v>381087</v>
       </c>
-      <c r="E11" s="7"/>
+      <c r="E11" s="7">
+        <v>50</v>
+      </c>
       <c r="F11" s="8"/>
     </row>
     <row r="12" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -676,7 +698,9 @@
       <c r="D12" s="6">
         <v>381084</v>
       </c>
-      <c r="E12" s="7"/>
+      <c r="E12" s="7">
+        <v>44</v>
+      </c>
       <c r="F12" s="8"/>
     </row>
     <row r="13" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -692,7 +716,9 @@
       <c r="D13" s="6">
         <v>381361</v>
       </c>
-      <c r="E13" s="7"/>
+      <c r="E13" s="7">
+        <v>30</v>
+      </c>
       <c r="F13" s="8"/>
     </row>
     <row r="14" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -708,7 +734,9 @@
       <c r="D14" s="6">
         <v>381085</v>
       </c>
-      <c r="E14" s="7"/>
+      <c r="E14" s="7">
+        <v>48</v>
+      </c>
       <c r="F14" s="8"/>
     </row>
     <row r="15" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -724,7 +752,9 @@
       <c r="D15" s="6">
         <v>381088</v>
       </c>
-      <c r="E15" s="7"/>
+      <c r="E15" s="7">
+        <v>48</v>
+      </c>
       <c r="F15" s="8"/>
     </row>
     <row r="16" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -740,7 +770,9 @@
       <c r="D16" s="6">
         <v>381089</v>
       </c>
-      <c r="E16" s="7"/>
+      <c r="E16" s="7">
+        <v>50</v>
+      </c>
       <c r="F16" s="8"/>
     </row>
     <row r="17" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -756,7 +788,9 @@
       <c r="D17" s="6">
         <v>381086</v>
       </c>
-      <c r="E17" s="7"/>
+      <c r="E17" s="7">
+        <v>36</v>
+      </c>
       <c r="F17" s="8"/>
     </row>
     <row r="18" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -772,7 +806,9 @@
       <c r="D18" s="6">
         <v>381360</v>
       </c>
-      <c r="E18" s="7"/>
+      <c r="E18" s="7">
+        <v>36</v>
+      </c>
       <c r="F18" s="8"/>
     </row>
     <row r="19" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -788,7 +824,9 @@
       <c r="D19" s="6">
         <v>381365</v>
       </c>
-      <c r="E19" s="7"/>
+      <c r="E19" s="7">
+        <v>47</v>
+      </c>
       <c r="F19" s="8"/>
     </row>
     <row r="20" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -804,7 +842,9 @@
       <c r="D20" s="6">
         <v>381364</v>
       </c>
-      <c r="E20" s="7"/>
+      <c r="E20" s="7">
+        <v>35</v>
+      </c>
       <c r="F20" s="8"/>
     </row>
     <row r="21" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -820,7 +860,9 @@
       <c r="D21" s="6">
         <v>381363</v>
       </c>
-      <c r="E21" s="7"/>
+      <c r="E21" s="7">
+        <v>48</v>
+      </c>
       <c r="F21" s="8"/>
     </row>
     <row r="22" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -836,7 +878,9 @@
       <c r="D22" s="6">
         <v>381366</v>
       </c>
-      <c r="E22" s="7"/>
+      <c r="E22" s="7">
+        <v>47</v>
+      </c>
       <c r="F22" s="8"/>
     </row>
     <row r="23" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -852,7 +896,9 @@
       <c r="D23" s="6">
         <v>381284</v>
       </c>
-      <c r="E23" s="7"/>
+      <c r="E23" s="7">
+        <v>50</v>
+      </c>
       <c r="F23" s="8"/>
     </row>
     <row r="24" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -868,7 +914,9 @@
       <c r="D24" s="6">
         <v>381283</v>
       </c>
-      <c r="E24" s="7"/>
+      <c r="E24" s="7">
+        <v>45</v>
+      </c>
       <c r="F24" s="8"/>
     </row>
     <row r="25" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -884,7 +932,9 @@
       <c r="D25" s="6">
         <v>381367</v>
       </c>
-      <c r="E25" s="7"/>
+      <c r="E25" s="7">
+        <v>40</v>
+      </c>
       <c r="F25" s="8"/>
     </row>
     <row r="26" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -900,7 +950,9 @@
       <c r="D26" s="6">
         <v>381092</v>
       </c>
-      <c r="E26" s="7"/>
+      <c r="E26" s="7">
+        <v>50</v>
+      </c>
       <c r="F26" s="8"/>
     </row>
     <row r="27" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -916,7 +968,9 @@
       <c r="D27" s="6">
         <v>381091</v>
       </c>
-      <c r="E27" s="7"/>
+      <c r="E27" s="7">
+        <v>48</v>
+      </c>
       <c r="F27" s="8"/>
     </row>
     <row r="28" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -932,7 +986,9 @@
       <c r="D28" s="6">
         <v>381708</v>
       </c>
-      <c r="E28" s="7"/>
+      <c r="E28" s="7">
+        <v>46</v>
+      </c>
       <c r="F28" s="8"/>
     </row>
     <row r="29" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -948,7 +1004,9 @@
       <c r="D29" s="6">
         <v>381804</v>
       </c>
-      <c r="E29" s="7"/>
+      <c r="E29" s="7">
+        <v>50</v>
+      </c>
       <c r="F29" s="8"/>
     </row>
     <row r="30" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -964,7 +1022,9 @@
       <c r="D30" s="6">
         <v>381294</v>
       </c>
-      <c r="E30" s="7"/>
+      <c r="E30" s="7">
+        <v>43</v>
+      </c>
       <c r="F30" s="8"/>
     </row>
     <row r="31" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -980,7 +1040,9 @@
       <c r="D31" s="6">
         <v>381402</v>
       </c>
-      <c r="E31" s="7"/>
+      <c r="E31" s="7">
+        <v>50</v>
+      </c>
       <c r="F31" s="8"/>
     </row>
     <row r="32" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -996,7 +1058,9 @@
       <c r="D32" s="6">
         <v>381377</v>
       </c>
-      <c r="E32" s="7"/>
+      <c r="E32" s="7">
+        <v>49</v>
+      </c>
       <c r="F32" s="8"/>
     </row>
     <row r="33" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1012,7 +1076,9 @@
       <c r="D33" s="6">
         <v>381287</v>
       </c>
-      <c r="E33" s="7"/>
+      <c r="E33" s="7">
+        <v>44</v>
+      </c>
       <c r="F33" s="8"/>
     </row>
     <row r="34" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1028,7 +1094,9 @@
       <c r="D34" s="6">
         <v>381286</v>
       </c>
-      <c r="E34" s="7"/>
+      <c r="E34" s="7">
+        <v>39</v>
+      </c>
       <c r="F34" s="8"/>
     </row>
     <row r="35" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1044,7 +1112,9 @@
       <c r="D35" s="6">
         <v>381285</v>
       </c>
-      <c r="E35" s="7"/>
+      <c r="E35" s="7">
+        <v>37</v>
+      </c>
       <c r="F35" s="8"/>
     </row>
     <row r="36" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1060,7 +1130,9 @@
       <c r="D36" s="6">
         <v>381636</v>
       </c>
-      <c r="E36" s="7"/>
+      <c r="E36" s="7">
+        <v>49</v>
+      </c>
       <c r="F36" s="8"/>
     </row>
     <row r="37" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1076,7 +1148,9 @@
       <c r="D37" s="6">
         <v>381637</v>
       </c>
-      <c r="E37" s="7"/>
+      <c r="E37" s="7">
+        <v>46</v>
+      </c>
       <c r="F37" s="8"/>
     </row>
     <row r="38" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1092,7 +1166,9 @@
       <c r="D38" s="6">
         <v>381368</v>
       </c>
-      <c r="E38" s="7"/>
+      <c r="E38" s="7">
+        <v>30</v>
+      </c>
       <c r="F38" s="8"/>
     </row>
     <row r="39" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1108,7 +1184,9 @@
       <c r="D39" s="6">
         <v>381288</v>
       </c>
-      <c r="E39" s="7"/>
+      <c r="E39" s="7">
+        <v>30</v>
+      </c>
       <c r="F39" s="8"/>
     </row>
     <row r="40" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1124,7 +1202,9 @@
       <c r="D40" s="6">
         <v>381638</v>
       </c>
-      <c r="E40" s="7"/>
+      <c r="E40" s="7">
+        <v>42</v>
+      </c>
       <c r="F40" s="8"/>
     </row>
     <row r="41" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1140,7 +1220,9 @@
       <c r="D41" s="6">
         <v>381639</v>
       </c>
-      <c r="E41" s="7"/>
+      <c r="E41" s="7">
+        <v>36</v>
+      </c>
       <c r="F41" s="8"/>
     </row>
     <row r="42" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1156,7 +1238,9 @@
       <c r="D42" s="6">
         <v>381371</v>
       </c>
-      <c r="E42" s="7"/>
+      <c r="E42" s="7">
+        <v>35</v>
+      </c>
       <c r="F42" s="8"/>
     </row>
     <row r="43" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1172,7 +1256,9 @@
       <c r="D43" s="6">
         <v>381370</v>
       </c>
-      <c r="E43" s="7"/>
+      <c r="E43" s="7">
+        <v>50</v>
+      </c>
       <c r="F43" s="8"/>
     </row>
     <row r="44" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1188,7 +1274,9 @@
       <c r="D44" s="6">
         <v>381369</v>
       </c>
-      <c r="E44" s="7"/>
+      <c r="E44" s="7">
+        <v>50</v>
+      </c>
       <c r="F44" s="8"/>
     </row>
     <row r="45" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1204,7 +1292,9 @@
       <c r="D45" s="6">
         <v>381094</v>
       </c>
-      <c r="E45" s="7"/>
+      <c r="E45" s="7">
+        <v>44</v>
+      </c>
       <c r="F45" s="8"/>
     </row>
     <row r="46" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1220,7 +1310,9 @@
       <c r="D46" s="6">
         <v>381095</v>
       </c>
-      <c r="E46" s="7"/>
+      <c r="E46" s="7">
+        <v>46</v>
+      </c>
       <c r="F46" s="8"/>
     </row>
     <row r="47" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1236,7 +1328,9 @@
       <c r="D47" s="6">
         <v>381373</v>
       </c>
-      <c r="E47" s="7"/>
+      <c r="E47" s="7">
+        <v>44</v>
+      </c>
       <c r="F47" s="8"/>
     </row>
     <row r="48" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1252,7 +1346,9 @@
       <c r="D48" s="6">
         <v>381712</v>
       </c>
-      <c r="E48" s="7"/>
+      <c r="E48" s="7">
+        <v>39</v>
+      </c>
       <c r="F48" s="8"/>
     </row>
     <row r="49" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1268,7 +1364,9 @@
       <c r="D49" s="6">
         <v>381096</v>
       </c>
-      <c r="E49" s="7"/>
+      <c r="E49" s="7">
+        <v>42</v>
+      </c>
       <c r="F49" s="8"/>
     </row>
     <row r="50" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1284,7 +1382,9 @@
       <c r="D50" s="6">
         <v>381379</v>
       </c>
-      <c r="E50" s="7"/>
+      <c r="E50" s="7">
+        <v>44</v>
+      </c>
       <c r="F50" s="8"/>
     </row>
     <row r="51" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1300,7 +1400,9 @@
       <c r="D51" s="6">
         <v>381807</v>
       </c>
-      <c r="E51" s="7"/>
+      <c r="E51" s="7">
+        <v>48</v>
+      </c>
       <c r="F51" s="8"/>
     </row>
     <row r="52" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1316,7 +1418,9 @@
       <c r="D52" s="6">
         <v>381713</v>
       </c>
-      <c r="E52" s="7"/>
+      <c r="E52" s="7">
+        <v>41</v>
+      </c>
       <c r="F52" s="8"/>
     </row>
     <row r="53" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1332,7 +1436,9 @@
       <c r="D53" s="6">
         <v>381378</v>
       </c>
-      <c r="E53" s="7"/>
+      <c r="E53" s="7">
+        <v>50</v>
+      </c>
       <c r="F53" s="8"/>
     </row>
     <row r="54" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1348,7 +1454,9 @@
       <c r="D54" s="6">
         <v>381290</v>
       </c>
-      <c r="E54" s="7"/>
+      <c r="E54" s="7">
+        <v>42</v>
+      </c>
       <c r="F54" s="8"/>
     </row>
     <row r="55" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1364,7 +1472,9 @@
       <c r="D55" s="6">
         <v>381100</v>
       </c>
-      <c r="E55" s="7"/>
+      <c r="E55" s="7">
+        <v>36</v>
+      </c>
       <c r="F55" s="8"/>
     </row>
     <row r="56" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1380,7 +1490,9 @@
       <c r="D56" s="6">
         <v>381291</v>
       </c>
-      <c r="E56" s="7"/>
+      <c r="E56" s="7">
+        <v>40</v>
+      </c>
       <c r="F56" s="8"/>
     </row>
     <row r="57" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1396,7 +1508,9 @@
       <c r="D57" s="6">
         <v>381701</v>
       </c>
-      <c r="E57" s="7"/>
+      <c r="E57" s="7">
+        <v>45</v>
+      </c>
       <c r="F57" s="8"/>
     </row>
     <row r="58" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1412,7 +1526,9 @@
       <c r="D58" s="6">
         <v>381289</v>
       </c>
-      <c r="E58" s="7"/>
+      <c r="E58" s="7">
+        <v>47</v>
+      </c>
       <c r="F58" s="8"/>
     </row>
     <row r="59" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1428,7 +1544,9 @@
       <c r="D59" s="6">
         <v>381292</v>
       </c>
-      <c r="E59" s="7"/>
+      <c r="E59" s="7">
+        <v>35</v>
+      </c>
       <c r="F59" s="8"/>
     </row>
     <row r="60" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1444,7 +1562,9 @@
       <c r="D60" s="6">
         <v>381293</v>
       </c>
-      <c r="E60" s="7"/>
+      <c r="E60" s="7">
+        <v>44</v>
+      </c>
       <c r="F60" s="8"/>
     </row>
     <row r="61" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1460,7 +1580,9 @@
       <c r="D61" s="6">
         <v>381803</v>
       </c>
-      <c r="E61" s="7"/>
+      <c r="E61" s="7">
+        <v>38</v>
+      </c>
       <c r="F61" s="8"/>
     </row>
     <row r="62" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1476,7 +1598,9 @@
       <c r="D62" s="6">
         <v>381808</v>
       </c>
-      <c r="E62" s="7"/>
+      <c r="E62" s="7">
+        <v>41</v>
+      </c>
       <c r="F62" s="8"/>
     </row>
     <row r="63" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1492,7 +1616,9 @@
       <c r="D63" s="6">
         <v>381295</v>
       </c>
-      <c r="E63" s="7"/>
+      <c r="E63" s="7">
+        <v>34</v>
+      </c>
       <c r="F63" s="8"/>
     </row>
     <row r="64" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1508,7 +1634,9 @@
       <c r="D64" s="6">
         <v>381296</v>
       </c>
-      <c r="E64" s="7"/>
+      <c r="E64" s="7">
+        <v>37</v>
+      </c>
       <c r="F64" s="8"/>
     </row>
     <row r="65" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1524,7 +1652,9 @@
       <c r="D65" s="10">
         <v>381299</v>
       </c>
-      <c r="E65" s="7"/>
+      <c r="E65" s="7">
+        <v>36</v>
+      </c>
       <c r="F65" s="8"/>
     </row>
     <row r="66" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1540,7 +1670,9 @@
       <c r="D66" s="10">
         <v>381375</v>
       </c>
-      <c r="E66" s="7"/>
+      <c r="E66" s="7">
+        <v>50</v>
+      </c>
       <c r="F66" s="8"/>
     </row>
     <row r="67" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1556,7 +1688,9 @@
       <c r="D67" s="10">
         <v>381376</v>
       </c>
-      <c r="E67" s="7"/>
+      <c r="E67" s="7">
+        <v>47</v>
+      </c>
       <c r="F67" s="8"/>
     </row>
     <row r="68" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1572,7 +1706,9 @@
       <c r="D68" s="10">
         <v>381374</v>
       </c>
-      <c r="E68" s="7"/>
+      <c r="E68" s="7">
+        <v>47</v>
+      </c>
       <c r="F68" s="8"/>
     </row>
     <row r="69" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1588,7 +1724,9 @@
       <c r="D69" s="10">
         <v>381703</v>
       </c>
-      <c r="E69" s="7"/>
+      <c r="E69" s="7">
+        <v>46</v>
+      </c>
       <c r="F69" s="8"/>
     </row>
     <row r="70" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1604,7 +1742,9 @@
       <c r="D70" s="10">
         <v>381704</v>
       </c>
-      <c r="E70" s="7"/>
+      <c r="E70" s="7">
+        <v>42</v>
+      </c>
       <c r="F70" s="8"/>
     </row>
     <row r="71" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1620,7 +1760,9 @@
       <c r="D71" s="10">
         <v>381702</v>
       </c>
-      <c r="E71" s="7"/>
+      <c r="E71" s="7">
+        <v>44</v>
+      </c>
       <c r="F71" s="11"/>
     </row>
     <row r="72" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1636,7 +1778,9 @@
       <c r="D72" s="10">
         <v>381706</v>
       </c>
-      <c r="E72" s="7"/>
+      <c r="E72" s="7">
+        <v>48</v>
+      </c>
       <c r="F72" s="11"/>
     </row>
     <row r="73" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1652,7 +1796,9 @@
       <c r="D73" s="10">
         <v>381707</v>
       </c>
-      <c r="E73" s="7"/>
+      <c r="E73" s="7">
+        <v>41</v>
+      </c>
       <c r="F73" s="11"/>
     </row>
     <row r="74" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1668,7 +1814,9 @@
       <c r="D74" s="10">
         <v>381705</v>
       </c>
-      <c r="E74" s="7"/>
+      <c r="E74" s="7">
+        <v>45</v>
+      </c>
       <c r="F74" s="11"/>
     </row>
     <row r="75" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1684,7 +1832,9 @@
       <c r="D75" s="10">
         <v>381709</v>
       </c>
-      <c r="E75" s="7"/>
+      <c r="E75" s="7">
+        <v>43</v>
+      </c>
       <c r="F75" s="11"/>
     </row>
     <row r="76" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1700,7 +1850,9 @@
       <c r="D76" s="10">
         <v>381710</v>
       </c>
-      <c r="E76" s="7"/>
+      <c r="E76" s="7">
+        <v>39</v>
+      </c>
       <c r="F76" s="11"/>
     </row>
     <row r="77" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1716,7 +1868,9 @@
       <c r="D77" s="10">
         <v>381380</v>
       </c>
-      <c r="E77" s="7"/>
+      <c r="E77" s="7">
+        <v>39</v>
+      </c>
       <c r="F77" s="11"/>
     </row>
     <row r="78" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1732,7 +1886,9 @@
       <c r="D78" s="10">
         <v>282389</v>
       </c>
-      <c r="E78" s="7"/>
+      <c r="E78" s="7">
+        <v>37</v>
+      </c>
       <c r="F78" s="11"/>
     </row>
     <row r="79" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1748,7 +1904,9 @@
       <c r="D79" s="10">
         <v>125889</v>
       </c>
-      <c r="E79" s="7"/>
+      <c r="E79" s="7">
+        <v>47</v>
+      </c>
       <c r="F79" s="11"/>
     </row>
     <row r="80" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1764,7 +1922,9 @@
       <c r="D80" s="10">
         <v>381298</v>
       </c>
-      <c r="E80" s="7"/>
+      <c r="E80" s="7">
+        <v>47</v>
+      </c>
       <c r="F80" s="11"/>
     </row>
     <row r="81" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1780,7 +1940,9 @@
       <c r="D81" s="10">
         <v>381711</v>
       </c>
-      <c r="E81" s="7"/>
+      <c r="E81" s="7">
+        <v>50</v>
+      </c>
       <c r="F81" s="11"/>
     </row>
     <row r="82" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1796,7 +1958,9 @@
       <c r="D82" s="10">
         <v>381297</v>
       </c>
-      <c r="E82" s="7"/>
+      <c r="E82" s="7">
+        <v>50</v>
+      </c>
       <c r="F82" s="11"/>
     </row>
     <row r="83" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1812,7 +1976,9 @@
       <c r="D83" s="10">
         <v>381802</v>
       </c>
-      <c r="E83" s="7"/>
+      <c r="E83" s="7">
+        <v>47</v>
+      </c>
       <c r="F83" s="11"/>
     </row>
     <row r="84" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1828,7 +1994,9 @@
       <c r="D84" s="10">
         <v>381805</v>
       </c>
-      <c r="E84" s="7"/>
+      <c r="E84" s="7">
+        <v>36</v>
+      </c>
       <c r="F84" s="11"/>
     </row>
     <row r="85" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1844,7 +2012,9 @@
       <c r="D85" s="10">
         <v>381806</v>
       </c>
-      <c r="E85" s="7"/>
+      <c r="E85" s="7">
+        <v>36</v>
+      </c>
       <c r="F85" s="11"/>
     </row>
     <row r="86" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1860,7 +2030,9 @@
       <c r="D86" s="10">
         <v>381300</v>
       </c>
-      <c r="E86" s="7"/>
+      <c r="E86" s="7">
+        <v>30</v>
+      </c>
       <c r="F86" s="11"/>
     </row>
     <row r="87" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1876,7 +2048,9 @@
       <c r="D87" s="10">
         <v>381801</v>
       </c>
-      <c r="E87" s="7"/>
+      <c r="E87" s="7">
+        <v>30</v>
+      </c>
       <c r="F87" s="11"/>
     </row>
     <row r="88" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1892,7 +2066,9 @@
       <c r="D88" s="10">
         <v>380886</v>
       </c>
-      <c r="E88" s="7"/>
+      <c r="E88" s="7">
+        <v>34</v>
+      </c>
       <c r="F88" s="11"/>
     </row>
     <row r="89" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1908,7 +2084,9 @@
       <c r="D89" s="10">
         <v>381403</v>
       </c>
-      <c r="E89" s="7"/>
+      <c r="E89" s="7">
+        <v>37</v>
+      </c>
       <c r="F89" s="11"/>
     </row>
     <row r="90" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1924,7 +2102,9 @@
       <c r="D90" s="10">
         <v>381090</v>
       </c>
-      <c r="E90" s="7"/>
+      <c r="E90" s="7">
+        <v>44</v>
+      </c>
       <c r="F90" s="11"/>
     </row>
     <row r="91" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1940,7 +2120,9 @@
       <c r="D91" s="10">
         <v>381093</v>
       </c>
-      <c r="E91" s="12"/>
+      <c r="E91" s="12">
+        <v>44</v>
+      </c>
       <c r="F91" s="11"/>
     </row>
     <row r="92" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -9106,8 +9288,8 @@
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="F3:F4"/>
   </mergeCells>
-  <pageMargins left="0.5" right="0.5" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageMargins left="0.59055118110236227" right="0.51181102362204722" top="0.39370078740157483" bottom="0.39370078740157483" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <rowBreaks count="28" manualBreakCount="28">
     <brk id="39" max="16383" man="1"/>
     <brk id="74" max="16383" man="1"/>
